--- a/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
+++ b/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
@@ -4477,7 +4477,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Shugaban gida</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Miji ko Matar aure</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Da ko 'Ya</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Uba ko Uwa</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Sauran dangi</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Ba dangi ba</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Shugaban gida</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Miji ko Matar aure</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Da ko 'Ya</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Uba ko Uwa</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Sauran dangi</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Ba dangi ba</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Kansa/Kanta</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Babu babba mai iya bayar da amsa bayan ziyara uku</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Gidan babu kowa ko an rushe shi</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Mai kula ko yaro ya ki</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Tsawo, kwance</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Tsawo, a tsaye</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>An ga katin, kwafinsa, ko bayanin lantarki</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Mai kula ya ki</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Mai kula ya ki</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Yaro ba ya nan</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Ba a iya samu ba</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Akwatin ya lalace</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Famfo a cikin gida</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Famfo a filin gida</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Famfon jama'a</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Rijiyar bututu</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Rijiya mai kariya</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Rijiya marar kariya</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Maɓulɓula mai kariya</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Maɓulɓula marar kariya</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Ruwan sama</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Ruwan tanka ko keken ruwa</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Ruwan bude (kogi ko tafki)</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Fasa ruwa zuwa magudanar ruwa</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Fasa ruwa zuwa tankin najasa</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Fasa ruwa zuwa rami</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Rami mai iska (VIP)</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Rami mai bene</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Rami marar bene</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Bayan gida na taki</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Bokiti</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Babu wurin, daji</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>An gani, akwai sabulu da ruwa</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>An fada kawai, ba a gani ba</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Rediyo</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Talabijin</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Wayar hannu</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Keke</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Babur</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Mota ko babbar mota</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Firji</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Babu ko daya daga cikin wadannan</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>A mayar don gyara</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 001 (TM01, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 002 (TM02, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 003 (TM03, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 004 (TM04, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 005 (TM05, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 006 (TM06, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 007 (TM07, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 008 (TM08, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 009 (TM09, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 010 (TM10, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 011 (TM11, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 012 (TM12, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 013 (TM13, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 014 (TM14, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 015 (TM15, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 016 (TM16, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 017 (TM17, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 018 (TM18, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 019 (TM19, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 020 (TM20, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 021 (TM21, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 022 (TM22, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 023 (TM23, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 024 (TM24, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 025 (TM01, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 026 (TM02, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 027 (TM03, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 028 (TM04, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 029 (TM05, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 030 (TM06, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 031 (TM07, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 032 (TM08, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 033 (TM09, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 034 (TM10, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 035 (TM11, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 036 (TM12, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 037 (TM13, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 038 (TM14, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 039 (TM15, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 040 (TM16, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 041 (TM17, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 042 (TM18, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 043 (TM19, Ilela)</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 044 (TM20, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 045 (TM21, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 046 (TM22, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 047 (TM23, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 048 (TM24, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 049 (TM01, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 050 (TM02, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 051 (TM03, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 052 (TM04, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 053 (TM05, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 054 (TM06, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 055 (TM07, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 056 (TM08, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 057 (TM09, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 058 (TM10, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 059 (TM11, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 060 (TM12, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 061 (TM13, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 062 (TM14, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 063 (TM15, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 064 (TM16, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 065 (TM17, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 066 (TM18, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 067 (TM19, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 068 (TM20, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 069 (TM21, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 070 (TM22, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 071 (TM23, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 072 (TM24, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 073 (TM01, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 074 (TM02, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 075 (TM03, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 076 (TM04, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 077 (TM05, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 078 (TM06, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 079 (TM07, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 080 (TM08, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 081 (TM09, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 082 (TM10, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 083 (TM11, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 084 (TM12, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 085 (TM13, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 086 (TM14, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 087 (TM15, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 088 (TM16, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 089 (TM17, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 090 (TM18, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 091 (TM19, Ilela)</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 092 (TM20, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 093 (TM21, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 094 (TM22, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 095 (TM23, Ilela)</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 096 (TM24, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 097 (TM01, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 098 (TM02, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 099 (TM03, Ilela)</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 100 (TM04, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 101 (TM05, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 102 (TM06, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 103 (TM07, Ilela)</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 104 (TM08, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 105 (TM09, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 106 (TM10, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 107 (TM11, Ilela)</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 108 (TM12, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 109 (TM13, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 110 (TM14, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 111 (TM15, Ilela)</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 112 (TM16, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 113 (TM17, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 114 (TM18, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 115 (TM19, Ilela)</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 116 (TM20, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 117 (TM21, Gwarin)</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 118 (TM22, Idi-Oro)</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 119 (TM23, Ilela)</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Enumerator 120 (TM24, Katsuma)</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
         </is>
       </c>
     </row>

--- a/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
+++ b/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
@@ -701,7 +701,11 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -767,7 +771,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
@@ -812,7 +820,11 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -882,7 +894,11 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1050,7 +1066,11 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1247,7 +1267,11 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1399,7 +1423,11 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1609,7 +1637,11 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -1930,7 +1962,11 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -1967,7 +2003,11 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -2012,7 +2052,11 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -2373,7 +2417,11 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -2459,7 +2507,11 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -2500,7 +2552,11 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -2586,7 +2642,11 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -2627,7 +2687,11 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
@@ -2668,7 +2732,11 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
@@ -2734,7 +2802,11 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
@@ -2771,7 +2843,11 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
@@ -2816,7 +2892,11 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
@@ -2898,7 +2978,11 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
@@ -2939,7 +3023,11 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
@@ -2976,7 +3064,11 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -3071,7 +3163,11 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
@@ -3265,11 +3361,7 @@
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>numbers</t>
-        </is>
-      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -3400,7 +3492,11 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
@@ -3673,7 +3769,11 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -3710,7 +3810,11 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
@@ -3747,7 +3851,11 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
@@ -3788,7 +3896,11 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
@@ -3825,7 +3937,11 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
@@ -3862,7 +3978,11 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
@@ -3907,7 +4027,11 @@
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>columns-2</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
@@ -4060,7 +4184,11 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
@@ -4097,7 +4225,11 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
@@ -4188,7 +4320,11 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
@@ -4221,7 +4357,11 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
@@ -8914,7 +9054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8943,6 +9083,11 @@
           <t>instance_name</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8968,6 +9113,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>concat(${lga_name_txt}, '-', ${settlement_code}, '-', ${structure_no}, '-', ${hh_serial})</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>theme-grid</t>
         </is>
       </c>
     </row>

--- a/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
+++ b/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,45 +451,55 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>guidance_hint::English (en)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>guidance_hint::Hausa (ha)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>required</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>constraint_message::English (en)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>appearance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>read_only</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>choice_filter</t>
         </is>
@@ -519,6 +529,8 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +556,8 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,6 +583,8 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,6 +610,8 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -627,6 +645,8 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -641,12 +661,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>1.01  State</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jiha</t>
+          <t>1.01  Jiha</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -657,13 +677,15 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -678,37 +700,43 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Local Government Area</t>
+          <t>1.02  Local Government Area</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kananan Hukuma</t>
+          <t>1.02  Kananan Hukuma</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Select from the administrative list. Do not type the name.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>Select from the list. Do not type the name.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Zaba daga jerin. Kada a rubuta sunan da hannu.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -729,15 +757,17 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>${lga}</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -752,33 +782,43 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>1.03  Ward</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Yankin gunduma</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>1.03  Yankin gunduma</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>List is filtered to the LGA you just selected.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jerin ya dogara ne akan Kananan Hukumar da aka zaba.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>lga_code=${lga}</t>
         </is>
@@ -797,12 +837,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Settlement</t>
+          <t>1.04  Settlement</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gari/kauye</t>
+          <t>1.04  Gari/kauye</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -810,24 +850,34 @@
           <t>Type a few letters to search. List has 2,524 entries -- do not scroll.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rubuta haruffa kadan don nema. Jerin yana da sunaye 2,524 -- kada a bi ta birgima.</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Filtered to the ward you just selected, and sourced directly from settlements.csv in the reference media -- record and code come from the same register the ministry supplied, not a re-typed list.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ward_code=${ward}</t>
         </is>
@@ -852,15 +902,17 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>${settlement}</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -875,33 +927,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Is the settlement known locally by a different name?</t>
+          <t>1.05  Is the settlement known locally by a different name?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shin mutanen yankin na kiran wannan wuri da wani suna daban?</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>1.05  Shin mutanen yankin na kiran wannan wuri da wani suna daban?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ask the respondent, do not assume from the register name alone.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>A tambayi wanda ake yi wa tambayoyi, kada a dogara da sunan da ke cikin rajista kadai.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>quick</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -927,18 +989,20 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>${settlement_local_name_known}='1'</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -953,37 +1017,47 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Structure number painted on the dwelling</t>
+          <t>1.06  Structure number painted on the dwelling</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lambar da aka rubuta a gidan</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>1.06  Lambar da aka rubuta a gidan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Copy the number exactly as painted. If none is painted, ask your supervisor before proceeding.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kwafi lambar daidai yadda take a rubuce. Idan babu lambar da aka rubuta, a tambayi mai kula kafin cigaba.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>. &gt;= 1 and . &lt;= 999</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Enter 1-999 (three digit box on the paper form).</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -998,37 +1072,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Household serial number within the settlement</t>
+          <t>1.07  Household serial number within the settlement</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lambar gida a cikin yankin</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>1.07  Lambar gida a cikin yankin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>The running count of households visited in this settlement -- your first household here is 1, second is 2, and so on.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Adadin gidajen da aka ziyarta a wannan yankin -- gidan farko shine 1, na biyu 2, da sauransu.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>. &gt;= 1 and . &lt;= 999</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Enter 1-999 (three digit box on the paper form).</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1043,37 +1127,43 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Enumerator code</t>
+          <t>1.08  Enumerator code</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lambar ma'aikaci</t>
+          <t>1.08  Lambar ma'aikaci</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Select your code from the staff list.</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>Select your own code from the staff list.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Zaba lambar kanka daga jerin ma'aikata.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1094,15 +1184,17 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>pulldata('staff_roster','team_code','name',${enumerator_code})</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1117,33 +1209,43 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Team code (auto-filled)</t>
+          <t>1.09  Team code (auto-filled)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lambar kungiya (kai tsaye)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+          <t>1.09  Lambar kungiya (kai tsaye)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Filled in automatically from your enumerator code -- nothing to type here.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ana cika wannan kai tsaye daga lambar ma'aikacinka -- babu abin da za a rubuta.</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>${team_code_auto}</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1158,37 +1260,47 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Date of visit</t>
+          <t>1.10  Date of visit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ranar ziyara</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>1.10  Ranar ziyara</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Must fall within the fieldwork period, 1-30 June 2026.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dole ranar ta kasance cikin kwanakin fieldwork, 1-30 Yuni 2026.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>. &gt;= date('2026-06-01') and . &lt;= date('2026-06-30')</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Date must fall within the fieldwork period printed on the form (1-30 June 2026).</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1203,37 +1315,51 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GPS reading at the entrance to the dwelling</t>
+          <t>1.11  GPS reading at the entrance to the dwelling</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wurin GPS a kofar gida</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+          <t>1.11  Wurin GPS a kofar gida</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Stand at the entrance to the dwelling and wait for the accuracy reading to settle before capturing.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tsaya a kofar gida kuma jira har lambar daidaito ta zauna kafin dauka.</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>A poor or indoor fix can be several hundred metres off. If the accuracy shown is worse than about 15m, step outside and try again before accepting the reading.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>number(substring-before(.,' ')) &gt;= 10.0 and number(substring-before(.,' ')) &lt;= 11.9 and number(substring-before(substring-after(.,' '),' ')) &gt;= 6.3 and number(substring-before(substring-after(.,' '),' ')) &lt;= 9.0</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Point falls outside the Bansara state working area. Re-take the reading.</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1248,33 +1374,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Was this household visited during the October 2025 round?</t>
+          <t>1.12  Was this household visited during the October 2025 round?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>An ziyarci wannan gida a lokacin 2025 ba?</t>
+          <t>1.12  An ziyarci wannan gida a lokacin 2025 ba?</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>quick</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1289,41 +1417,51 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Household identifier allocated in the October 2025 round</t>
+          <t>1.13  Household identifier allocated in the October 2025 round</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lambar da aka bawa gida a 2025</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>1.13  Lambar da aka bawa gida a 2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Format BAN-000000, copied from the previous round's paperwork or supervisor list.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tsari BAN-000000, an kwafo daga takardun zagayen da ya gabata ko jerin mai kula.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>${prev_round_visited}='1'</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>regex(., '^BAN-[0-9]{6}$') and pulldata('previous_round_households','household_id','household_id',.) != ''</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Format must be BAN-000000 and must match an identifier in the previous round register.</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1344,15 +1482,17 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>if(${prev_round_visited}='1', pulldata('previous_round_households','children_under5_last_round','household_id',${prev_round_hh_id}), '')</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1378,18 +1518,20 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>${prev_round_visited}='1' and ${prev_round_children_u5}!=''</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1404,33 +1546,43 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Result of visit</t>
+          <t>1.14  Result of visit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sakamakon ziyara</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>1.14  Sakamakon ziyara</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>If the result is anything other than Completed, sign at 7.03 and submit -- do not continue to later sections.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Idan sakamakon ba An kammala ba, a sa hannu a 7.03 sannan a mika -- kada a ci gaba da sauran kashi.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1452,6 +1604,8 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1477,18 +1631,20 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>${visit_result}='2' or ${visit_result}='3' or ${visit_result}='4'</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1514,18 +1670,20 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>${visit_result}='1'</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1540,29 +1698,39 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Consent statement read aloud to the respondent in full?</t>
+          <t>2.01  Consent statement read aloud to the respondent in full?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>An karanta bayanin yardar shiga gaba daya ga wanda ake tambaya?</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>2.01  An karanta bayanin yardar shiga gaba daya ga wanda ake tambaya?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Read the printed consent script exactly as written. Do not summarise or paraphrase it.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>A karanta rubutun yardar shiga daidai yadda yake, kada a takaita ko a canza kalmomi.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1577,29 +1745,39 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Does the respondent consent to the household interview?</t>
+          <t>2.02  Does the respondent consent to the household interview?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wanda ake tambaya ya yarda a yi hira da gidan?</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>2.02  Wanda ake tambaya ya yarda a yi hira da gidan?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>If refused, thank the respondent, sign at 7.03, and submit -- no further section is completed.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Idan an ki, a gode wa wanda ake tambaya, a sa hannu a 7.03, sannan a mika -- babu wani kashi da za a ci gaba da shi.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1614,37 +1792,39 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Relationship of the respondent to the head of household</t>
+          <t>2.03  Relationship of the respondent to the head of household</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Dangantakar wanda ake tambaya da shugaban gida</t>
+          <t>2.03  Dangantakar wanda ake tambaya da shugaban gida</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>${consent_given}='1'</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1666,6 +1846,8 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1691,18 +1873,20 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>${visit_result}='1' and ${consent_given}='2'</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1728,18 +1912,20 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>${visit_result}='1' and ${consent_given}='1'</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1754,37 +1940,47 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>How many people usually live in this household?</t>
+          <t>3.01  How many people usually live in this household?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mutane nawa suke zaune a wannan gida?</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>3.01  Mutane nawa suke zaune a wannan gida?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ask this before listing the roster below. A usual resident is someone who normally sleeps here, even if temporarily away.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>A tambayi wannan kafin jera mutane a kasa. Mutumin da yake zaune yana nufin wanda yake barci a nan a saba, ko da yake ba ya nan yanzu na dan lokaci.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>. &gt;= 1 and . &lt;= 30</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Enter 1-30. If genuinely larger, flag for supervisor at 7.02.</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1818,6 +2014,8 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1851,6 +2049,8 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1865,12 +2065,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Line number</t>
+          <t>(1)  Line number</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lamba</t>
+          <t>(1)  Lamba</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1879,19 +2079,21 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
         <is>
           <t>position(..)</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1906,29 +2108,39 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Name or initials</t>
+          <t>(2)  Name or initials</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Suna ko gajerun haruffa</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>(2)  Suna ko gajerun haruffa</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Initials are acceptable and preferred where a full name is not needed for the interview.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ana iya amfani da gajerun haruffa maimakon cikakken suna idan ba a bukata a cikin hira.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1943,33 +2155,35 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Relationship to head</t>
+          <t>(3)  Relationship to head</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Dangantaka da shugaban gida</t>
+          <t>(3)  Dangantaka da shugaban gida</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1984,33 +2198,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>(4)  Sex</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Jinsi</t>
+          <t>(4)  Jinsi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2035,7 +2251,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Not on the paper form -- added so the digital form routes to the correct age field. See defects report D-02.</t>
+          <t>Not on the paper form -- added so the digital form routes to column (5) or (6) correctly. See defects report D-02.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2043,23 +2259,25 @@
           <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2074,41 +2292,51 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Age in completed years</t>
+          <t>(5)  Age in completed years</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Shekaru cikakku</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>(5)  Shekaru cikakku</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Completed years -- round down, do not round up to the nearest birthday.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Shekaru cikakku -- a rage zuwa kasa, kada a kara zuwa ranar haihuwa mai zuwa.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>${member_under5}='2'</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>. &gt;= 5 and . &lt;= 110</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Enter 5-110 years.</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2123,41 +2351,51 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Age in completed months (under five only)</t>
+          <t>(6)  Age in completed months (under five only)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Watanni cikakku (kasa da shekara biyar kadai)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>(6)  Watanni cikakku (kasa da shekara biyar kadai)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>If exact age is not known, estimate using a local events/seasonal calendar rather than guessing.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Idan ba a san ainihin shekaru ba, a yi kiyasi ta amfani da abubuwan da suka faru a yankin ko lokutan shekara, kada a yi tsammani kawai.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>${member_under5}='1'</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>. &gt;= 0 and . &lt;= 59</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Enter 0-59 completed months.</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2178,15 +2416,17 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
         <is>
           <t>if(${member_under5}='1' and ${age_months} &gt;= 9 and ${age_months} &lt;= 59, 1, 0)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2212,18 +2452,20 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>${eligible_s4}=1</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2249,18 +2491,20 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
         <is>
           <t>${eligible_s4}=1</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2275,12 +2519,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Name or initials of the child (copied from roster)</t>
+          <t>4.02  Name or initials of the child (copied from roster)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sunan yaro (an dauko daga jeri)</t>
+          <t>4.02  Sunan yaro (an dauko daga jeri)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2289,19 +2533,21 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
         <is>
           <t>${member_name}</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2316,12 +2562,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Age of the child in completed months (copied from roster)</t>
+          <t>4.03  Age of the child in completed months (copied from roster)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Shekarun yaro da watanni (an dauko daga jeri)</t>
+          <t>4.03  Shekarun yaro da watanni (an dauko daga jeri)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2330,19 +2576,21 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
         <is>
           <t>${age_months}</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2357,12 +2605,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sex of the child (copied from roster)</t>
+          <t>4.04  Sex of the child (copied from roster)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Jinsin yaro (an dauko daga jeri)</t>
+          <t>4.04  Jinsin yaro (an dauko daga jeri)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2371,19 +2619,21 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
         <is>
           <t>${member_sex}</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2398,33 +2648,43 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Weight measurement status</t>
+          <t>4.05  Weight measurement status</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Halin auna nauyi</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>4.05  Halin auna nauyi</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Paper question 4.05 asked for the weight itself, with 99 meaning not measured. Here that is two separate fields -- pick the status first.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2439,41 +2699,51 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Weight of the child (kg)</t>
+          <t>4.05  Weight of the child (kg)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nauyin yaro (kg)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>4.05  Nauyin yaro (kg)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Record to the nearest 0.1 kg, with the child in light clothing.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>A rubuta zuwa 0.1 kg mafi kusa, yaro na sanye da tufafi masu sauki.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>${weight_status}='1'</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>. &gt;= 2.0 and . &lt;= 30.0</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Enter 2.0-30.0 kg.</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2488,33 +2758,43 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Length/height measurement status</t>
+          <t>4.06  Length/height measurement status</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Halin auna tsawo</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>4.06  Halin auna tsawo</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Paper question 4.06 asked for the measurement itself, with 99 meaning not measured. Here that is two separate fields -- pick the status first.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2529,37 +2809,51 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Position in which the child was measured</t>
+          <t>4.07  Position in which the child was measured</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Yanayin da aka auna yaro</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+          <t>4.07  Yanayin da aka auna yaro</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>A change part-way through the round is expected -- record what was actually used, do not force consistency with earlier children.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ana sa ran za a canza yayin zagayen -- a rubuta abin da aka yi amfani da shi na gaskiya, kada a tilasta daidaituwa da sauran yara.</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>WHO/DHS convention: measure children under 24 months recumbent (lying down); measure children 24 months and older standing, unless the child cannot stand, in which case use recumbent and note it at 7.02.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>${height_status}='1'</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2574,41 +2868,51 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Length or height of the child (cm)</t>
+          <t>4.06  Length or height of the child (cm)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tsawon yaro (cm)</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>4.06  Tsawon yaro (cm)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Record to the nearest 0.1 cm.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>A rubuta zuwa 0.1 cm mafi kusa.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>${height_status}='1'</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>. &gt;= 45.0 and . &lt;= 130.0</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Enter 45.0-130.0 cm.</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2623,33 +2927,43 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>May I see the child's vaccination card or health record?</t>
+          <t>4.08  May I see the child's vaccination card or health record?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Zan iya ganin katin allurar yaro ko bayanin lafiyarsa?</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>4.08  Zan iya ganin katin allurar yaro ko bayanin lafiyarsa?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ask to see the actual card or electronic record before answering -- do not accept a verbal description as 'seen.'</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>A nemi ganin ainihin katin ko bayanin lantarki kafin amsawa -- kada a karbi bayanin baki a matsayin an gani.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2664,37 +2978,47 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Copy from the card: is a measles dose recorded?</t>
+          <t>4.09  Copy from the card: is a measles dose recorded?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Daga kati: an rubuta an yi wa yaro allurar kyanda?</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>4.09  Daga kati: an rubuta an yi wa yaro allurar kyanda?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Record exactly what is written on the card -- do not ask the caregiver to recall this one, the card is in front of you.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>A rubuta daidai abin da ke rubuce a kati -- kada a tambayi mai kula game da wannan, kati na gabanka ne.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>${vacc_card_seen}='1'</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2709,37 +3033,39 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Has this child ever received a measles vaccination?</t>
+          <t>4.10  Has this child ever received a measles vaccination?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Yaro ya taba samun allurar kyanda?</t>
+          <t>4.10  Yaro ya taba samun allurar kyanda?</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>${vacc_card_seen}='2'</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2760,15 +3086,17 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
         <is>
           <t>if(${vacc_card_seen}='1', ${measles_from_card}, ${measles_recall})</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2783,33 +3111,43 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Has this child had diarrhoea in the past 14 days?</t>
+          <t>4.11  Has this child had diarrhoea in the past 14 days?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Yaro ya sha gudawa cikin kwanaki 14 da suka wuce?</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>4.11  Yaro ya sha gudawa cikin kwanaki 14 da suka wuce?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Diarrhoea means three or more loose or watery stools in 24 hours.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gudawa yana nufin fitsi mai laushi ko ruwa sau uku ko fiye a cikin awa 24.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2824,33 +3162,35 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Has this child taken any antibiotic medicine in the past 30 days?</t>
+          <t>4.12  Has this child taken any antibiotic medicine in the past 30 days?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Yaro ya sha maganin rigakafin kwayoyin cuta cikin kwanaki 30 da suka wuce?</t>
+          <t>4.12  Yaro ya sha maganin rigakafin kwayoyin cuta cikin kwanaki 30 da suka wuce?</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2865,41 +3205,51 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Which antibiotic was taken?</t>
+          <t>4.13  Which antibiotic was taken?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wanne maganin rigakafi ne aka sha?</t>
+          <t>4.13  Wanne maganin rigakafi ne aka sha?</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PLACEHOLDER LIST -- the data pack did not include the ministry medicine list referenced by the paper form. See defects report D-05.</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>If more than one was taken, record the most recent.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Idan an sha fiye da daya, a rubuta wanda aka sha kwanan nan.</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>PLACEHOLDER LIST -- the data pack supplied for this assessment did not include the ministry's medicine/antimicrobial code list referenced by the paper form at 4.13. This list is an illustrative stand-in only (WHO AWaRe-informed common oral/injectable antibiotics) and must be replaced with the actual ministry AMR technical working group list before deployment -- see defects report D-05.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>${antibiotic_30d}='1'</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2914,33 +3264,35 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>If Other, write the name of the medicine as reported</t>
+          <t>4.14  If Other, write the name of the medicine as reported</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Idan Wani, rubuta sunan maganin</t>
+          <t>4.14  Idan Wani, rubuta sunan maganin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>${antibiotic_code}='96'</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2955,37 +3307,39 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Was the medicine obtained without a prescription from a health worker?</t>
+          <t>4.15  Was the medicine obtained without a prescription from a health worker?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>An sami maganin ba tare da takardar likita ba?</t>
+          <t>4.15  An sami maganin ba tare da takardar likita ba?</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>${antibiotic_30d}='1'</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3000,37 +3354,47 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Was a photograph of the medicine packaging taken?</t>
+          <t>4.16  Was a photograph of the medicine packaging taken?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>An dauki hoton fakitin magani?</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>4.16  An dauki hoton fakitin magani?</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ask the caregiver's permission before photographing the packaging.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>A nemi izinin mai kula kafin daukar hoton fakitin.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>${antibiotic_30d}='1'</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3045,33 +3409,43 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Photograph of medicine packaging</t>
+          <t>4.16  Photograph of medicine packaging</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Hoton fakitin magani</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+          <t>4.16  Hoton fakitin magani</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Take a clear, well-lit photo showing the medicine name on the packaging.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>A dauki hoto mai haske da bayyanawa wanda ke nuna sunan maganin a fakitin.</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
         <is>
           <t>${antibiotic_photo}='1'</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3093,6 +3467,8 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3118,18 +3494,20 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
         <is>
           <t>${eligible_s4}=1 and ${age_months} &gt;= 12</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3144,33 +3522,43 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Was a stool specimen obtained from this child?</t>
+          <t>5.02  Was a stool specimen obtained from this child?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>An samu samfurin kashin yaro?</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>5.02  An samu samfurin kashin yaro?</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>If Yes, you will label and store it next. If No, you will record why below.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Idan Ee, za a manna lambar sannan a adana samfurin. Idan A'a, za a rubuta dalili a kasa.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3191,15 +3579,17 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
         <is>
           <t>pulldata('specimen_label_allocation','range_start','team_code',${team_code_auto})</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3220,15 +3610,17 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
         <is>
           <t>pulldata('specimen_label_allocation','range_end','team_code',${team_code_auto})</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3249,15 +3641,17 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
         <is>
           <t>substr(${specimen_label},3,6)</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3278,15 +3672,17 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
         <is>
           <t>number(substr(${label_digits},0,1))*7 + number(substr(${label_digits},1,1))*6 + number(substr(${label_digits},2,1))*5 + number(substr(${label_digits},3,1))*4 + number(substr(${label_digits},4,1))*3 + number(substr(${label_digits},5,1))*2</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3307,15 +3703,17 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
         <is>
           <t>if((${label_checksum} mod 11)=10, 'X', string(${label_checksum} mod 11))</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3330,41 +3728,55 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Specimen label number (affix label, then transcribe in full)</t>
+          <t>5.03  Specimen label number (affix label, then transcribe in full)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lambar samfurin (a manne sannan a rubuta gaba daya)</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+          <t>5.03  Lambar samfurin (a manne sannan a rubuta gaba daya)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Affix the label to the specimen container first, then type the full code exactly as printed, including the letter/digit after the dash.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>A fara manna lambar akan akwatin samfurin, sannan a rubuta cikakkiyar lambar daidai yadda take a buga, har da harafi/lamba bayan dash din.</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>Format BSN######-C. The last character (a digit or the letter X) is a check digit computed from the six digits before it -- the form verifies it automatically and will reject a mistyped label, so re-check the physical label carefully before assuming the form is wrong.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>${specimen_obtained}='1'</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>regex(., '^BSN[0-9]{6}-[0-9X]$') and number(substr(.,3,6)) &gt;= number(${label_range_start}) and number(substr(.,3,6)) &lt;= number(${label_range_end}) and substr(.,10,1) = ${label_check_expected} and count(../../../roster/specimen/specimen_label[. = current()]) &lt;= 1</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>Label must be format BSN######-C, in your team's allocated range, with a valid check digit, and not already used for another child in this same household submission.</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3379,33 +3791,43 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Time the specimen was placed in the cold box</t>
+          <t>5.04  Time the specimen was placed in the cold box</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lokacin da aka sa samfurin cikin akwatin sanyi</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>5.04  Lokacin da aka sa samfurin cikin akwatin sanyi</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>24-hour clock, e.g. 14:30 for 2:30pm.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Agogon awa 24, misali 14:30 don karfe 2:30 na yamma.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>${specimen_obtained}='1'</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3420,41 +3842,51 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Temperature shown on the cold box thermometer</t>
+          <t>5.05  Temperature shown on the cold box thermometer</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Zafin da ke akwatin sanyi</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>5.05  Zafin da ke akwatin sanyi</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Read directly from the thermometer at the moment the specimen is placed inside.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>A karanta kai tsaye daga thermometer a lokacin da aka sa samfurin a ciki.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>${specimen_obtained}='1'</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>. &gt;= 0.0 and . &lt;= 12.0</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>Enter 0.0-12.0 degrees C.</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3469,37 +3901,39 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Reason no specimen was obtained</t>
+          <t>5.06  Reason no specimen was obtained</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Dalilin da ba a samu samfurin ba</t>
+          <t>5.06  Dalilin da ba a samu samfurin ba</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>${specimen_obtained}='2'</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3514,33 +3948,35 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>If Other, specify</t>
+          <t>5.07  If Other, specify</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Idan Wani, bayyana</t>
+          <t>5.07  Idan Wani, bayyana</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>${specimen_no_reason}='96'</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3562,6 +3998,8 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3583,6 +4021,8 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3603,15 +4043,17 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
         <is>
           <t>count(${roster})</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3632,15 +4074,17 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
         <is>
           <t>if(${hh_size_stated} != ${roster_count_actual}, 1, 0)</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3666,18 +4110,20 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
         <is>
           <t>${hh_size_stated} != ${roster_count_actual}</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3699,6 +4145,8 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3724,18 +4172,20 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
         <is>
           <t>${visit_result}='1' and ${consent_given}='1'</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3750,33 +4200,43 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Main source of drinking water</t>
+          <t>6.01  Main source of drinking water</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Babban tushen ruwan sha</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>6.01  Babban tushen ruwan sha</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>The source used most of the time, not an occasional backup source.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tushen da ake amfani da shi mafi yawan lokaci, ba wanda ake amfani da shi lokaci lokaci ba.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3791,33 +4251,35 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kind of toilet facility usually used</t>
+          <t>6.02  Kind of toilet facility usually used</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Irin bayan gida da ake amfani da shi</t>
+          <t>6.02  Irin bayan gida da ake amfani da shi</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3832,33 +4294,35 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Does this household keep poultry or livestock inside the compound?</t>
+          <t>6.03  Does this household keep poultry or livestock inside the compound?</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Gidan yana da kaji ko dabbobi a cikin gida?</t>
+          <t>6.03  Gidan yana da kaji ko dabbobi a cikin gida?</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
         <is>
           <t>quick</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3873,37 +4337,39 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Have any antibiotic medicines been given to these animals in the past 12 months?</t>
+          <t>6.04  Have any antibiotic medicines been given to these animals in the past 12 months?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>An bawa dabbobin magungunan rigakafi cikin watanni 12 da suka wuce?</t>
+          <t>6.04  An bawa dabbobin magungunan rigakafi cikin watanni 12 da suka wuce?</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>${livestock_in_compound}='1'</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
         <is>
           <t>quick</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3918,33 +4384,43 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Handwashing station with soap and water available?</t>
+          <t>6.05  Handwashing station with soap and water available?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Akwai wurin wanke hannu da sabulu da ruwa?</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>6.05  Akwai wurin wanke hannu da sabulu da ruwa?</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ask to see the handwashing place -- do not just ask the question and accept a verbal answer.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>A nemi ganin wurin wanke hannu -- kada kawai a tambaya a karbi amsa ta baki.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
         <is>
           <t>quick</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3959,33 +4435,35 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Has any member of this household had diarrhoea in the past two weeks?</t>
+          <t>6.06  Has any member of this household had diarrhoea in the past two weeks?</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wani a gida ya sha gudawa cikin makonni biyu da suka wuce?</t>
+          <t>6.06  Wani a gida ya sha gudawa cikin makonni biyu da suka wuce?</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr">
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
         <is>
           <t>quick</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4000,41 +4478,51 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Which of the following does this household own?</t>
+          <t>6.07  Which of the following does this household own?</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wanne daga cikin wadannan gidan yake da su?</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>6.07  Wanne daga cikin wadannan gidan yake da su?</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Select every item this household owns. Select 'None of these' only if none apply.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>A zaba duk abin da gidan yake da shi. A zaba 'Babu ko daya' idan babu wanda ya dace.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>not(selected(., 'H')) or count-selected(.)=1</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>'None of these' cannot be selected together with any other item.</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
         <is>
           <t>columns-2</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4056,6 +4544,8 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4081,18 +4571,20 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
         <is>
           <t>${visit_result}='1' and ${consent_given}='1'</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4113,15 +4605,17 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
         <is>
           <t>(decimal-date-time(${end}) - decimal-date-time(${start})) * 1440</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4155,6 +4649,8 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4169,29 +4665,39 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Observation that may help the office interpret this form</t>
+          <t>7.02  Observation that may help the office interpret this form</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Bayani da zai taimaka wa ofis</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+          <t>7.02  Bayani da zai taimaka wa ofis</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Do not record the respondent's name or other identifying detail here -- see data-protection notes.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Kada a rubuta sunan wanda ake tambaya ko wani bayani da zai bayyana shi a nan.</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr">
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
         <is>
           <t>multiline</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4206,33 +4712,35 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Enumerator signature (select your code again to confirm)</t>
+          <t>7.03  Enumerator signature (select your code again to confirm)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tabbatar da lambar ka</t>
+          <t>7.03  Tabbatar da lambar ka</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr">
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4254,6 +4762,8 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4283,14 +4793,16 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4305,12 +4817,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Supervisor code</t>
+          <t>7.04  Supervisor code</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Lambar mai kula</t>
+          <t>7.04  Lambar mai kula</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4320,14 +4832,16 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4342,12 +4856,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Supervisor decision on this form</t>
+          <t>7.05  Supervisor decision on this form</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Shawarar mai kula</t>
+          <t>7.05  Shawarar mai kula</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4357,14 +4871,16 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr">
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4386,6 +4902,8 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
+++ b/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
@@ -3215,17 +3215,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>If more than one was taken, record the most recent.</t>
+          <t>If more than one was taken, record the most recent. NOTE: this list is a placeholder -- see the info icon.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Idan an sha fiye da daya, a rubuta wanda aka sha kwanan nan.</t>
+          <t>Idan an sha fiye da daya, a rubuta wanda aka sha kwanan nan. LURA: wannan jeri na dan lokaci ne kawai -- duba alamar bayani.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PLACEHOLDER LIST -- the data pack supplied for this assessment did not include the ministry's medicine/antimicrobial code list referenced by the paper form at 4.13. This list is an illustrative stand-in only (WHO AWaRe-informed common oral/injectable antibiotics) and must be replaced with the actual ministry AMR technical working group list before deployment -- see defects report D-05.</t>
+          <t>PLACEHOLDER LIST -- the data pack supplied for this assessment did not include the ministry's medicine/antimicrobial code list referenced by the paper form at 4.13. The 13 medicine names below are a real, illustrative WHO AWaRe-informed list of common oral/injectable antibiotics (not invented drug names), but this is not the ministry's approved formulary code list and must be replaced with it before deployment -- see defects report D-05. The disclosure is kept here, at the field level, rather than repeated on every choice option, so the running form stays legible during testing.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -9266,12 +9266,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Amoxicillin</t>
+          <t>Amoxicillin</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Amoxicillin</t>
         </is>
       </c>
     </row>
@@ -9288,12 +9288,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Amoxicillin-clavulanate</t>
+          <t>Amoxicillin-clavulanate</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Amoxicillin-clavulanate</t>
         </is>
       </c>
     </row>
@@ -9310,12 +9310,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Co-trimoxazole (sulfamethoxazole-trimethoprim)</t>
+          <t>Co-trimoxazole (sulfamethoxazole-trimethoprim)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Co-trimoxazole (sulfamethoxazole-trimethoprim)</t>
         </is>
       </c>
     </row>
@@ -9332,12 +9332,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Ampicillin</t>
+          <t>Ampicillin</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Ampicillin</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Ampicillin-cloxacillin combination</t>
+          <t>Ampicillin-cloxacillin combination</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Ampicillin-cloxacillin combination</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Erythromycin</t>
+          <t>Erythromycin</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Erythromycin</t>
         </is>
       </c>
     </row>
@@ -9398,12 +9398,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Cefixime</t>
+          <t>Cefixime</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Cefixime</t>
         </is>
       </c>
     </row>
@@ -9420,12 +9420,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Cefuroxime</t>
+          <t>Cefuroxime</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Cefuroxime</t>
         </is>
       </c>
     </row>
@@ -9442,12 +9442,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Ciprofloxacin</t>
+          <t>Ciprofloxacin</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Ciprofloxacin</t>
         </is>
       </c>
     </row>
@@ -9464,12 +9464,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Metronidazole</t>
+          <t>Metronidazole</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Metronidazole</t>
         </is>
       </c>
     </row>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Gentamicin (injectable)</t>
+          <t>Gentamicin (injectable)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Gentamicin (injectable)</t>
         </is>
       </c>
     </row>
@@ -9508,12 +9508,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Chloramphenicol</t>
+          <t>Chloramphenicol</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Chloramphenicol</t>
         </is>
       </c>
     </row>
@@ -9530,12 +9530,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER] Doxycycline/Tetracycline</t>
+          <t>Doxycycline/Tetracycline</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[JERI BAI ISA BA — ana jira daga Ma'aikatar Lafiya]</t>
+          <t>Doxycycline/Tetracycline</t>
         </is>
       </c>
     </row>

--- a/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
+++ b/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q105"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3195,7 +3195,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>select_one medicine_list</t>
+          <t>select_one_from_file medicine_list.csv</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>If more than one was taken, record the most recent. NOTE: this list is a placeholder -- see the info icon.</t>
+          <t>This question cannot be answered yet -- the medicine list has not been supplied. See the info icon.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Idan an sha fiye da daya, a rubuta wanda aka sha kwanan nan. LURA: wannan jeri na dan lokaci ne kawai -- duba alamar bayani.</t>
+          <t>Ba za a iya amsa wannan tambaya ba tukuna -- ba a bayar da jerin magunguna ba. Duba alamar bayani.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PLACEHOLDER LIST -- the data pack supplied for this assessment did not include the ministry's medicine/antimicrobial code list referenced by the paper form at 4.13. The 13 medicine names below are a real, illustrative WHO AWaRe-informed list of common oral/injectable antibiotics (not invented drug names), but this is not the ministry's approved formulary code list and must be replaced with it before deployment -- see defects report D-05. The disclosure is kept here, at the field level, rather than repeated on every choice option, so the running form stays legible during testing.</t>
+          <t>Question 4.13 on the paper form instructs: 'Record from the medicine list.' No medicine/antimicrobial code list was supplied anywhere in the data pack for this assessment -- confirmed by directory listing and a full-text search of reference_media/. This field is wired exactly like the LGA/Ward/Settlement selects (select_one_from_file against an external CSV attached as form media), but form/media/medicine_list.csv is a stub -- a header row only (name,label columns), no data. The ministry/AMR technical working group needs to supply the actual coded list; once medicine_list.csv is populated with real rows and reattached, this question works with no other change to the form. Until then it correctly has no answer to offer. See defects report D-05.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -3254,22 +3254,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>antibiotic_other</t>
+          <t>antibiotic_no_rx</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>4.14  If Other, write the name of the medicine as reported</t>
+          <t>4.15  Was the medicine obtained without a prescription from a health worker?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4.14  Idan Wani, rubuta sunan maganin</t>
+          <t>4.15  An sami maganin ba tare da takardar likita ba?</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3283,13 +3283,17 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>${antibiotic_code}='96'</t>
+          <t>${antibiotic_30d}='1'</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
@@ -3297,26 +3301,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one photo_status</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>antibiotic_no_rx</t>
+          <t>antibiotic_photo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4.15  Was the medicine obtained without a prescription from a health worker?</t>
+          <t>4.16  Was a photograph of the medicine packaging taken?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4.15  An sami maganin ba tare da takardar likita ba?</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+          <t>4.16  An dauki hoton fakitin magani?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ask the caregiver's permission before photographing the packaging.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>A nemi izinin mai kula kafin daukar hoton fakitin.</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
@@ -3344,44 +3356,40 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>select_one photo_status</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>antibiotic_photo</t>
+          <t>antibiotic_photo_file</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>4.16  Was a photograph of the medicine packaging taken?</t>
+          <t>4.16  Photograph of medicine packaging</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4.16  An dauki hoton fakitin magani?</t>
+          <t>4.16  Hoton fakitin magani</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ask the caregiver's permission before photographing the packaging.</t>
+          <t>Take a clear, well-lit photo showing the medicine name on the packaging.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>A nemi izinin mai kula kafin daukar hoton fakitin.</t>
+          <t>A dauki hoto mai haske da bayyanawa wanda ke nuna sunan maganin a fakitin.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>${antibiotic_30d}='1'</t>
+          <t>${antibiotic_photo}='1'</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -3389,7 +3397,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>new</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -3399,50 +3407,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>antibiotic_photo_file</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>4.16  Photograph of medicine packaging</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>4.16  Hoton fakitin magani</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Take a clear, well-lit photo showing the medicine name on the packaging.</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>A dauki hoto mai haske da bayyanawa wanda ke nuna sunan maganin a fakitin.</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>${antibiotic_photo}='1'</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
@@ -3450,18 +3430,34 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>specimen</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Section 5: Specimen collection</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kashi na 5: Tattara samfurin</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>${eligible_s4}=1 and ${age_months} &gt;= 12</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -3473,38 +3469,50 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>specimen</t>
+          <t>specimen_obtained</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Section 5: Specimen collection</t>
+          <t>5.02  Was a stool specimen obtained from this child?</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kashi na 5: Tattara samfurin</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+          <t>5.02  An samu samfurin kashin yaro?</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>If Yes, you will label and store it next. If No, you will record why below.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Idan Ee, za a manna lambar sannan a adana samfurin. Idan A'a, za a rubuta dalili a kasa.</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>${eligible_s4}=1 and ${age_months} &gt;= 12</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
@@ -3512,50 +3520,30 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>specimen_obtained</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>5.02  Was a stool specimen obtained from this child?</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>5.02  An samu samfurin kashin yaro?</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>If Yes, you will label and store it next. If No, you will record why below.</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Idan Ee, za a manna lambar sannan a adana samfurin. Idan A'a, za a rubuta dalili a kasa.</t>
-        </is>
-      </c>
+          <t>label_range_start</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>pulldata('specimen_label_allocation','range_start','team_code',${team_code_auto})</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
@@ -3568,7 +3556,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>label_range_start</t>
+          <t>label_range_end</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -3583,7 +3571,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>pulldata('specimen_label_allocation','range_start','team_code',${team_code_auto})</t>
+          <t>pulldata('specimen_label_allocation','range_end','team_code',${team_code_auto})</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -3599,7 +3587,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>label_range_end</t>
+          <t>label_digits</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -3614,7 +3602,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>pulldata('specimen_label_allocation','range_end','team_code',${team_code_auto})</t>
+          <t>substr(${specimen_label},3,6)</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -3630,7 +3618,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>label_digits</t>
+          <t>label_checksum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -3645,7 +3633,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>substr(${specimen_label},3,6)</t>
+          <t>number(substr(${label_digits},0,1))*7 + number(substr(${label_digits},1,1))*6 + number(substr(${label_digits},2,1))*5 + number(substr(${label_digits},3,1))*4 + number(substr(${label_digits},4,1))*3 + number(substr(${label_digits},5,1))*2</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -3661,7 +3649,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>label_checksum</t>
+          <t>label_check_expected</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -3676,7 +3664,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>number(substr(${label_digits},0,1))*7 + number(substr(${label_digits},1,1))*6 + number(substr(${label_digits},2,1))*5 + number(substr(${label_digits},3,1))*4 + number(substr(${label_digits},4,1))*3 + number(substr(${label_digits},5,1))*2</t>
+          <t>if((${label_checksum} mod 11)=10, 'X', string(${label_checksum} mod 11))</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -3687,29 +3675,61 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>label_check_expected</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+          <t>specimen_label</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>5.03  Specimen label number (affix label, then transcribe in full)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>5.03  Lambar samfurin (a manne sannan a rubuta gaba daya)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Affix the label to the specimen container first, then type the full code exactly as printed, including the letter/digit after the dash.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>A fara manna lambar akan akwatin samfurin, sannan a rubuta cikakkiyar lambar daidai yadda take a buga, har da harafi/lamba bayan dash din.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Format BSN######-C. The last character (a digit or the letter X) is a check digit computed from the six digits before it -- the form verifies it automatically and will reject a mistyped label, so re-check the physical label carefully before assuming the form is wrong.</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>if((${label_checksum} mod 11)=10, 'X', string(${label_checksum} mod 11))</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>${specimen_obtained}='1'</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>regex(., '^BSN[0-9]{6}-[0-9X]$') and number(substr(.,3,6)) &gt;= number(${label_range_start}) and number(substr(.,3,6)) &lt;= number(${label_range_end}) and substr(.,10,1) = ${label_check_expected} and count(../../../roster/specimen/specimen_label[. = current()]) &lt;= 1</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Label must be format BSN######-C, in your team's allocated range, with a valid check digit, and not already used for another child in this same household submission.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
@@ -3718,39 +3738,35 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>specimen_label</t>
+          <t>specimen_cold_box_time</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5.03  Specimen label number (affix label, then transcribe in full)</t>
+          <t>5.04  Time the specimen was placed in the cold box</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5.03  Lambar samfurin (a manne sannan a rubuta gaba daya)</t>
+          <t>5.04  Lokacin da aka sa samfurin cikin akwatin sanyi</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Affix the label to the specimen container first, then type the full code exactly as printed, including the letter/digit after the dash.</t>
+          <t>24-hour clock, e.g. 14:30 for 2:30pm.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>A fara manna lambar akan akwatin samfurin, sannan a rubuta cikakkiyar lambar daidai yadda take a buga, har da harafi/lamba bayan dash din.</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Format BSN######-C. The last character (a digit or the letter X) is a check digit computed from the six digits before it -- the form verifies it automatically and will reject a mistyped label, so re-check the physical label carefully before assuming the form is wrong.</t>
-        </is>
-      </c>
+          <t>Agogon awa 24, misali 14:30 don karfe 2:30 na yamma.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
@@ -3762,16 +3778,8 @@
           <t>${specimen_obtained}='1'</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>regex(., '^BSN[0-9]{6}-[0-9X]$') and number(substr(.,3,6)) &gt;= number(${label_range_start}) and number(substr(.,3,6)) &lt;= number(${label_range_end}) and substr(.,10,1) = ${label_check_expected} and count(../../../roster/specimen/specimen_label[. = current()]) &lt;= 1</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Label must be format BSN######-C, in your team's allocated range, with a valid check digit, and not already used for another child in this same household submission.</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
@@ -3781,32 +3789,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>specimen_cold_box_time</t>
+          <t>specimen_temp_c</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5.04  Time the specimen was placed in the cold box</t>
+          <t>5.05  Temperature shown on the cold box thermometer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5.04  Lokacin da aka sa samfurin cikin akwatin sanyi</t>
+          <t>5.05  Zafin da ke akwatin sanyi</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>24-hour clock, e.g. 14:30 for 2:30pm.</t>
+          <t>Read directly from the thermometer at the moment the specimen is placed inside.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Agogon awa 24, misali 14:30 don karfe 2:30 na yamma.</t>
+          <t>A karanta kai tsaye daga thermometer a lokacin da aka sa samfurin a ciki.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -3821,8 +3829,16 @@
           <t>${specimen_obtained}='1'</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>. &gt;= 0.0 and . &lt;= 12.0</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Enter 0.0-12.0 degrees C.</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
@@ -3832,34 +3848,26 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one no_specimen_reason</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>specimen_temp_c</t>
+          <t>specimen_no_reason</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5.05  Temperature shown on the cold box thermometer</t>
+          <t>5.06  Reason no specimen was obtained</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.05  Zafin da ke akwatin sanyi</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Read directly from the thermometer at the moment the specimen is placed inside.</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>A karanta kai tsaye daga thermometer a lokacin da aka sa samfurin a ciki.</t>
-        </is>
-      </c>
+          <t>5.06  Dalilin da ba a samu samfurin ba</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
@@ -3869,21 +3877,17 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>${specimen_obtained}='1'</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>. &gt;= 0.0 and . &lt;= 12.0</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Enter 0.0-12.0 degrees C.</t>
-        </is>
-      </c>
+          <t>${specimen_obtained}='2'</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
@@ -3891,22 +3895,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>select_one no_specimen_reason</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>specimen_no_reason</t>
+          <t>specimen_no_reason_other</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>5.06  Reason no specimen was obtained</t>
+          <t>5.07  If Other, specify</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5.06  Dalilin da ba a samu samfurin ba</t>
+          <t>5.07  Idan Wani, bayyana</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3920,17 +3924,13 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>${specimen_obtained}='2'</t>
+          <t>${specimen_no_reason}='96'</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
@@ -3938,38 +3938,18 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>specimen_no_reason_other</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>5.07  If Other, specify</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>5.07  Idan Wani, bayyana</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>${specimen_no_reason}='96'</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -3981,7 +3961,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>end group</t>
+          <t>end repeat</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -4004,10 +3984,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>end repeat</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>roster_count_actual</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -4018,7 +4002,11 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>count(${roster})</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
@@ -4032,7 +4020,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>roster_count_actual</t>
+          <t>roster_mismatch_flag</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -4047,7 +4035,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>count(${roster})</t>
+          <t>if(${hh_size_stated} != ${roster_count_actual}, 1, 0)</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -4058,29 +4046,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>roster_mismatch_flag</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+          <t>roster_vs_stated_note</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Stated household size was ${hh_size_stated}. The roster you just completed lists ${roster_count_actual} people. Please recheck before continuing if these differ.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>${hh_size_stated} != ${roster_count_actual}</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>if(${hh_size_stated} != ${roster_count_actual}, 1, 0)</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
@@ -4089,34 +4085,18 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>roster_vs_stated_note</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Stated household size was ${hh_size_stated}. The roster you just completed lists ${roster_count_actual} people. Please recheck before continuing if these differ.</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>${hh_size_stated} != ${roster_count_actual}</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
@@ -4128,18 +4108,34 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>s6</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Section 6: Household environment</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Kashi na 6: Muhallin gida</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>${visit_result}='1' and ${consent_given}='1'</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
@@ -4151,38 +4147,50 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one water_source</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>s6</t>
+          <t>water_source</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Section 6: Household environment</t>
+          <t>6.01  Main source of drinking water</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Kashi na 6: Muhallin gida</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+          <t>6.01  Babban tushen ruwan sha</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>The source used most of the time, not an occasional backup source.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tushen da ake amfani da shi mafi yawan lokaci, ba wanda ake amfani da shi lokaci lokaci ba.</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>${visit_result}='1' and ${consent_given}='1'</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
@@ -4190,34 +4198,26 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>select_one water_source</t>
+          <t>select_one toilet_type</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>water_source</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>6.01  Main source of drinking water</t>
+          <t>6.02  Kind of toilet facility usually used</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6.01  Babban tushen ruwan sha</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>The source used most of the time, not an occasional backup source.</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Tushen da ake amfani da shi mafi yawan lokaci, ba wanda ake amfani da shi lokaci lokaci ba.</t>
-        </is>
-      </c>
+          <t>6.02  Irin bayan gida da ake amfani da shi</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
@@ -4241,22 +4241,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>select_one toilet_type</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>livestock_in_compound</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>6.02  Kind of toilet facility usually used</t>
+          <t>6.03  Does this household keep poultry or livestock inside the compound?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6.02  Irin bayan gida da ake amfani da shi</t>
+          <t>6.03  Gidan yana da kaji ko dabbobi a cikin gida?</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -4274,7 +4274,7 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>quick</t>
         </is>
       </c>
       <c r="O89" t="inlineStr"/>
@@ -4284,22 +4284,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>livestock_in_compound</t>
+          <t>animal_antibiotics_12m</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>6.03  Does this household keep poultry or livestock inside the compound?</t>
+          <t>6.04  Have any antibiotic medicines been given to these animals in the past 12 months?</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6.03  Gidan yana da kaji ko dabbobi a cikin gida?</t>
+          <t>6.04  An bawa dabbobin magungunan rigakafi cikin watanni 12 da suka wuce?</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -4311,7 +4311,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>${livestock_in_compound}='1'</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
@@ -4327,26 +4331,34 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one handwash</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>animal_antibiotics_12m</t>
+          <t>handwash_station</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>6.04  Have any antibiotic medicines been given to these animals in the past 12 months?</t>
+          <t>6.05  Handwashing station with soap and water available?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6.04  An bawa dabbobin magungunan rigakafi cikin watanni 12 da suka wuce?</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+          <t>6.05  Akwai wurin wanke hannu da sabulu da ruwa?</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Ask to see the handwashing place -- do not just ask the question and accept a verbal answer.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>A nemi ganin wurin wanke hannu -- kada kawai a tambaya a karbi amsa ta baki.</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
@@ -4354,11 +4366,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>${livestock_in_compound}='1'</t>
-        </is>
-      </c>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
@@ -4374,34 +4382,26 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>select_one handwash</t>
+          <t>select_one yes_no_dk</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>handwash_station</t>
+          <t>hh_diarrhoea_2w</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>6.05  Handwashing station with soap and water available?</t>
+          <t>6.06  Has any member of this household had diarrhoea in the past two weeks?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6.05  Akwai wurin wanke hannu da sabulu da ruwa?</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Ask to see the handwashing place -- do not just ask the question and accept a verbal answer.</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>A nemi ganin wurin wanke hannu -- kada kawai a tambaya a karbi amsa ta baki.</t>
-        </is>
-      </c>
+          <t>6.06  Wani a gida ya sha gudawa cikin makonni biyu da suka wuce?</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
@@ -4425,26 +4425,34 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_multiple assets</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>hh_diarrhoea_2w</t>
+          <t>hh_assets</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>6.06  Has any member of this household had diarrhoea in the past two weeks?</t>
+          <t>6.07  Which of the following does this household own?</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6.06  Wani a gida ya sha gudawa cikin makonni biyu da suka wuce?</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+          <t>6.07  Wanne daga cikin wadannan gidan yake da su?</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Select every item this household owns. Select 'None of these' only if none apply.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>A zaba duk abin da gidan yake da shi. A zaba 'Babu ko daya' idan babu wanda ya dace.</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
@@ -4453,12 +4461,20 @@
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>not(selected(., 'H')) or count-selected(.)=1</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be selected together with any other item.</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>quick</t>
+          <t>columns-2</t>
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
@@ -4468,58 +4484,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>select_multiple assets</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>hh_assets</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>6.07  Which of the following does this household own?</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>6.07  Wanne daga cikin wadannan gidan yake da su?</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Select every item this household owns. Select 'None of these' only if none apply.</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>A zaba duk abin da gidan yake da shi. A zaba 'Babu ko daya' idan babu wanda ya dace.</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>not(selected(., 'H')) or count-selected(.)=1</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>'None of these' cannot be selected together with any other item.</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>columns-2</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
@@ -4527,18 +4507,34 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>s7</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Section 7: Close-out and supervisor review</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Kashi na 7: Kammalawa</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>${visit_result}='1' and ${consent_given}='1'</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
@@ -4550,37 +4546,29 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>s7</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Section 7: Close-out and supervisor review</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Kashi na 7: Kammalawa</t>
-        </is>
-      </c>
+          <t>duration_minutes</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>${visit_result}='1' and ${consent_given}='1'</t>
-        </is>
-      </c>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>(decimal-date-time(${end}) - decimal-date-time(${start})) * 1440</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
@@ -4589,16 +4577,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>duration_minutes</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+          <t>interview_end_note</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Interview end time is captured automatically when you submit; the form no longer asks you to type it separately (paper 7.01). See defects report and fabrication-detection doc.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
@@ -4607,11 +4603,7 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>(decimal-date-time(${end}) - decimal-date-time(${start})) * 1440</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
@@ -4620,26 +4612,34 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>interview_end_note</t>
+          <t>supervisor_note</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Interview end time is captured automatically when you submit; the form no longer asks you to type it separately (paper 7.01). See defects report and fabrication-detection doc.</t>
+          <t>7.02  Observation that may help the office interpret this form</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+          <t>7.02  Bayani da zai taimaka wa ofis</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Do not record the respondent's name or other identifying detail here -- see data-protection notes.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kada a rubuta sunan wanda ake tambaya ko wani bayani da zai bayyana shi a nan.</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
@@ -4647,7 +4647,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
@@ -4655,44 +4659,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one enumerator</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>supervisor_note</t>
+          <t>supervisor_signoff_enum_code</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>7.02  Observation that may help the office interpret this form</t>
+          <t>7.03  Enumerator signature (select your code again to confirm)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7.02  Bayani da zai taimaka wa ofis</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Do not record the respondent's name or other identifying detail here -- see data-protection notes.</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Kada a rubuta sunan wanda ake tambaya ko wani bayani da zai bayyana shi a nan.</t>
-        </is>
-      </c>
+          <t>7.03  Tabbatar da lambar ka</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
-          <t>multiline</t>
+          <t>minimal</t>
         </is>
       </c>
       <c r="O99" t="inlineStr"/>
@@ -4702,42 +4702,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>select_one enumerator</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>supervisor_signoff_enum_code</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>7.03  Enumerator signature (select your code again to confirm)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>7.03  Tabbatar da lambar ka</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
@@ -4745,12 +4725,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>s7sup</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Supervisor review (completed after handover, not by the enumerator)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Bitar mai kula</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
@@ -4760,7 +4752,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
@@ -4768,22 +4764,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one enumerator</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>s7sup</t>
+          <t>supervisor_code</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Supervisor review (completed after handover, not by the enumerator)</t>
+          <t>7.04  Supervisor code</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Bitar mai kula</t>
+          <t>7.04  Lambar mai kula</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -4797,7 +4793,7 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
-          <t>field-list</t>
+          <t>minimal</t>
         </is>
       </c>
       <c r="O102" t="inlineStr"/>
@@ -4807,22 +4803,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_one enumerator</t>
+          <t>select_one supervisor_decision</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>supervisor_code</t>
+          <t>supervisor_decision</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.04  Supervisor code</t>
+          <t>7.05  Supervisor decision on this form</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7.04  Lambar mai kula</t>
+          <t>7.05  Shawarar mai kula</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4846,24 +4842,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>select_one supervisor_decision</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>supervisor_decision</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>7.05  Supervisor decision on this form</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>7.05  Shawarar mai kula</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
@@ -4873,37 +4857,10 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4916,7 +4873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9250,314 +9207,6 @@
       <c r="D197" t="inlineStr">
         <is>
           <t>Enumerator 120 (TM24, Katsuma)</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Amoxicillin</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Amoxicillin</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Amoxicillin-clavulanate</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Amoxicillin-clavulanate</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Co-trimoxazole (sulfamethoxazole-trimethoprim)</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Co-trimoxazole (sulfamethoxazole-trimethoprim)</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Ampicillin</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Ampicillin</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Ampicillin-cloxacillin combination</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Ampicillin-cloxacillin combination</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Erythromycin</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Erythromycin</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Cefixime</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Cefixime</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Cefuroxime</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Cefuroxime</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Ciprofloxacin</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Ciprofloxacin</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Metronidazole</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Metronidazole</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Gentamicin (injectable)</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Gentamicin (injectable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Chloramphenicol</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Chloramphenicol</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Doxycycline/Tetracycline</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Doxycycline/Tetracycline</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>medicine_list</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Wani</t>
         </is>
       </c>
     </row>

--- a/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
+++ b/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026060100</t>
+          <t>2026073100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
+++ b/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
@@ -4530,11 +4530,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>${visit_result}='1' and ${consent_given}='1'</t>
-        </is>
-      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
@@ -9269,7 +9265,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026073100</t>
+          <t>2026073101</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
+++ b/Q3_Digital_Form_Development/form/HH2026_v1.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="entities" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +503,11 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>choice_filter</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>save_to</t>
         </is>
       </c>
     </row>
@@ -531,6 +537,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -558,6 +565,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -585,6 +593,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -612,6 +621,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -647,6 +657,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -686,6 +697,7 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -737,6 +749,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -768,6 +781,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -823,6 +837,7 @@
           <t>lga_code=${lga}</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -882,6 +897,7 @@
           <t>ward_code=${ward}</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -913,6 +929,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -964,6 +981,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1003,6 +1021,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1058,6 +1077,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1113,6 +1133,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1164,6 +1185,7 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1195,6 +1217,7 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1246,6 +1269,7 @@
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1301,6 +1325,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1360,6 +1385,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1403,6 +1429,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1462,6 +1489,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1493,6 +1521,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1532,6 +1561,7 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1583,6 +1613,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1606,6 +1637,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1645,6 +1677,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1684,6 +1717,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1731,6 +1765,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1778,6 +1813,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1825,6 +1861,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1848,6 +1885,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1887,6 +1925,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1926,6 +1965,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1981,6 +2021,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2016,6 +2057,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2051,6 +2093,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2094,6 +2137,7 @@
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2141,6 +2185,7 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2184,6 +2229,7 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2227,6 +2273,7 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2278,6 +2325,7 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2337,6 +2385,7 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2396,6 +2445,7 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2427,6 +2477,7 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2466,6 +2517,7 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2505,6 +2557,7 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2548,6 +2601,7 @@
         </is>
       </c>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2591,6 +2645,7 @@
         </is>
       </c>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2634,6 +2689,7 @@
         </is>
       </c>
       <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2685,6 +2741,7 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2744,6 +2801,7 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2795,6 +2853,7 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2854,6 +2913,7 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2913,6 +2973,7 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2964,6 +3025,7 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3019,6 +3081,7 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3066,6 +3129,7 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3097,6 +3161,7 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3148,6 +3213,7 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3191,6 +3257,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3250,6 +3317,7 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3297,6 +3365,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3352,6 +3421,7 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3403,6 +3473,7 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3426,6 +3497,7 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3465,6 +3537,7 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3516,6 +3589,7 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3547,6 +3621,7 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3578,6 +3653,7 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3609,6 +3685,7 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3640,6 +3717,7 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3671,6 +3749,7 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3721,12 +3800,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>regex(., '^BSN[0-9]{6}-[0-9X]$') and number(substr(.,3,6)) &gt;= number(${label_range_start}) and number(substr(.,3,6)) &lt;= number(${label_range_end}) and substr(.,10,1) = ${label_check_expected} and count(../../../roster/specimen/specimen_label[. = current()]) &lt;= 1</t>
+          <t>regex(., '^BSN[0-9]{6}-[0-9X]$') and number(substr(.,3,6)) &gt;= number(${label_range_start}) and number(substr(.,3,6)) &lt;= number(${label_range_end}) and substr(.,10,1) = ${label_check_expected} and count(../../../roster/specimen/specimen_label[. = current()]) &lt;= 1 and count(instance('used_specimen_labels')/root/item[specimen_label_value = current()]) = 0</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Label must be format BSN######-C, in your team's allocated range, with a valid check digit, and not already used for another child in this same household submission.</t>
+          <t>Label must be format BSN######-C, in your team's allocated range, with a valid check digit, not already used for another child in this same household submission, and not already used in an earlier submission on this device.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -3734,140 +3813,115 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>specimen_label_value</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>specimen_cold_box_time</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>5.04  Time the specimen was placed in the cold box</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>5.04  Lokacin da aka sa samfurin cikin akwatin sanyi</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>24-hour clock, e.g. 14:30 for 2:30pm.</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Agogon awa 24, misali 14:30 don karfe 2:30 na yamma.</t>
-        </is>
-      </c>
+          <t>specimen_device_id_for_entity</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>${specimen_obtained}='1'</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>${device_id}</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>device_id_value</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>specimen_temp_c</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>5.05  Temperature shown on the cold box thermometer</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>5.05  Zafin da ke akwatin sanyi</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Read directly from the thermometer at the moment the specimen is placed inside.</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>A karanta kai tsaye daga thermometer a lokacin da aka sa samfurin a ciki.</t>
-        </is>
-      </c>
+          <t>specimen_label_saved_at</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>${specimen_obtained}='1'</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>. &gt;= 0.0 and . &lt;= 12.0</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Enter 0.0-12.0 degrees C.</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>entered_at</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>select_one no_specimen_reason</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>specimen_no_reason</t>
+          <t>specimen_cold_box_time</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5.06  Reason no specimen was obtained</t>
+          <t>5.04  Time the specimen was placed in the cold box</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5.06  Dalilin da ba a samu samfurin ba</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+          <t>5.04  Lokacin da aka sa samfurin cikin akwatin sanyi</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>24-hour clock, e.g. 14:30 for 2:30pm.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Agogon awa 24, misali 14:30 don karfe 2:30 na yamma.</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
@@ -3877,44 +3931,49 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>${specimen_obtained}='2'</t>
+          <t>${specimen_obtained}='1'</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>specimen_no_reason_other</t>
+          <t>specimen_temp_c</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>5.07  If Other, specify</t>
+          <t>5.05  Temperature shown on the cold box thermometer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5.07  Idan Wani, bayyana</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+          <t>5.05  Zafin da ke akwatin sanyi</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Read directly from the thermometer at the moment the specimen is placed inside.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>A karanta kai tsaye daga thermometer a lokacin da aka sa samfurin a ciki.</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
@@ -3924,55 +3983,109 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>${specimen_no_reason}='96'</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
+          <t>${specimen_obtained}='1'</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>. &gt;= 0.0 and . &lt;= 12.0</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Enter 0.0-12.0 degrees C.</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
+          <t>select_one no_specimen_reason</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>specimen_no_reason</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>5.06  Reason no specimen was obtained</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5.06  Dalilin da ba a samu samfurin ba</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>${specimen_obtained}='2'</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>end repeat</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>specimen_no_reason_other</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>5.07  If Other, specify</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>5.07  Idan Wani, bayyana</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>${specimen_no_reason}='96'</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
@@ -3980,18 +4093,15 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>roster_count_actual</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -4002,27 +4112,20 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>count(${roster})</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>roster_mismatch_flag</t>
-        </is>
-      </c>
+          <t>end repeat</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -4033,62 +4136,56 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>if(${hh_size_stated} != ${roster_count_actual}, 1, 0)</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>roster_vs_stated_note</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Stated household size was ${hh_size_stated}. The roster you just completed lists ${roster_count_actual} people. Please recheck before continuing if these differ.</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
-        </is>
-      </c>
+          <t>roster_count_actual</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>${hh_size_stated} != ${roster_count_actual}</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>count(${roster})</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>roster_mismatch_flag</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -4099,31 +4196,36 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>if(${hh_size_stated} != ${roster_count_actual}, 1, 0)</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>s6</t>
+          <t>roster_vs_stated_note</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Section 6: Household environment</t>
+          <t>Stated household size was ${hh_size_stated}. The roster you just completed lists ${roster_count_actual} people. Please recheck before continuing if these differ.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Kashi na 6: Muhallin gida</t>
+          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4133,7 +4235,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>${visit_result}='1' and ${consent_given}='1'</t>
+          <t>${hh_size_stated} != ${roster_count_actual}</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -4143,124 +4245,103 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>select_one water_source</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>water_source</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>6.01  Main source of drinking water</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>6.01  Babban tushen ruwan sha</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>The source used most of the time, not an occasional backup source.</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Tushen da ake amfani da shi mafi yawan lokaci, ba wanda ake amfani da shi lokaci lokaci ba.</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>select_one toilet_type</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>s6</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>6.02  Kind of toilet facility usually used</t>
+          <t>Section 6: Household environment</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6.02  Irin bayan gida da ake amfani da shi</t>
+          <t>Kashi na 6: Muhallin gida</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>${visit_result}='1' and ${consent_given}='1'</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>select_one yes_no</t>
+          <t>select_one water_source</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>livestock_in_compound</t>
+          <t>water_source</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>6.03  Does this household keep poultry or livestock inside the compound?</t>
+          <t>6.01  Main source of drinking water</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6.03  Gidan yana da kaji ko dabbobi a cikin gida?</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+          <t>6.01  Babban tushen ruwan sha</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>The source used most of the time, not an occasional backup source.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tushen da ake amfani da shi mafi yawan lokaci, ba wanda ake amfani da shi lokaci lokaci ba.</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
@@ -4274,32 +4355,33 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
-          <t>quick</t>
+          <t>minimal</t>
         </is>
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>select_one yes_no_dk</t>
+          <t>select_one toilet_type</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>animal_antibiotics_12m</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>6.04  Have any antibiotic medicines been given to these animals in the past 12 months?</t>
+          <t>6.02  Kind of toilet facility usually used</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6.04  An bawa dabbobin magungunan rigakafi cikin watanni 12 da suka wuce?</t>
+          <t>6.02  Irin bayan gida da ake amfani da shi</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -4311,54 +4393,43 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>${livestock_in_compound}='1'</t>
-        </is>
-      </c>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>quick</t>
+          <t>minimal</t>
         </is>
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>select_one handwash</t>
+          <t>select_one yes_no</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>handwash_station</t>
+          <t>livestock_in_compound</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>6.05  Handwashing station with soap and water available?</t>
+          <t>6.03  Does this household keep poultry or livestock inside the compound?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6.05  Akwai wurin wanke hannu da sabulu da ruwa?</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Ask to see the handwashing place -- do not just ask the question and accept a verbal answer.</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>A nemi ganin wurin wanke hannu -- kada kawai a tambaya a karbi amsa ta baki.</t>
-        </is>
-      </c>
+          <t>6.03  Gidan yana da kaji ko dabbobi a cikin gida?</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
@@ -4378,6 +4449,7 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4387,17 +4459,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>hh_diarrhoea_2w</t>
+          <t>animal_antibiotics_12m</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>6.06  Has any member of this household had diarrhoea in the past two weeks?</t>
+          <t>6.04  Have any antibiotic medicines been given to these animals in the past 12 months?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6.06  Wani a gida ya sha gudawa cikin makonni biyu da suka wuce?</t>
+          <t>6.04  An bawa dabbobin magungunan rigakafi cikin watanni 12 da suka wuce?</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4409,7 +4481,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>${livestock_in_compound}='1'</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
@@ -4421,36 +4497,37 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>select_multiple assets</t>
+          <t>select_one handwash</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>hh_assets</t>
+          <t>handwash_station</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>6.07  Which of the following does this household own?</t>
+          <t>6.05  Handwashing station with soap and water available?</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6.07  Wanne daga cikin wadannan gidan yake da su?</t>
+          <t>6.05  Akwai wurin wanke hannu da sabulu da ruwa?</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Select every item this household owns. Select 'None of these' only if none apply.</t>
+          <t>Ask to see the handwashing place -- do not just ask the question and accept a verbal answer.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>A zaba duk abin da gidan yake da shi. A zaba 'Babu ko daya' idan babu wanda ya dace.</t>
+          <t>A nemi ganin wurin wanke hannu -- kada kawai a tambaya a karbi amsa ta baki.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -4461,95 +4538,130 @@
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>not(selected(., 'H')) or count-selected(.)=1</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>'None of these' cannot be selected together with any other item.</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
-          <t>columns-2</t>
+          <t>quick</t>
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+          <t>select_one yes_no_dk</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>hh_diarrhoea_2w</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>6.06  Has any member of this household had diarrhoea in the past two weeks?</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>6.06  Wani a gida ya sha gudawa cikin makonni biyu da suka wuce?</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_multiple assets</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>s7</t>
+          <t>hh_assets</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Section 7: Close-out and supervisor review</t>
+          <t>6.07  Which of the following does this household own?</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Kashi na 7: Kammalawa</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+          <t>6.07  Wanne daga cikin wadannan gidan yake da su?</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Select every item this household owns. Select 'None of these' only if none apply.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>A zaba duk abin da gidan yake da shi. A zaba 'Babu ko daya' idan babu wanda ya dace.</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>not(selected(., 'H')) or count-selected(.)=1</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be selected together with any other item.</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>columns-2</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>duration_minutes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -4560,35 +4672,32 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>(decimal-date-time(${end}) - decimal-date-time(${start})) * 1440</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>interview_end_note</t>
+          <t>s7</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Interview end time is captured automatically when you submit; the form no longer asks you to type it separately (paper 7.01). See defects report and fabrication-detection doc.</t>
+          <t>Section 7: Close-out and supervisor review</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
+          <t>Kashi na 7: Kammalawa</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -4604,108 +4713,107 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>supervisor_note</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>7.02  Observation that may help the office interpret this form</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>7.02  Bayani da zai taimaka wa ofis</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Do not record the respondent's name or other identifying detail here -- see data-protection notes.</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Kada a rubuta sunan wanda ake tambaya ko wani bayani da zai bayyana shi a nan.</t>
-        </is>
-      </c>
+          <t>duration_minutes</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>multiline</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>(decimal-date-time(${end}) - decimal-date-time(${start})) * 1440</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>select_one enumerator</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>supervisor_signoff_enum_code</t>
+          <t>interview_end_note</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>7.03  Enumerator signature (select your code again to confirm)</t>
+          <t>Interview end time is captured automatically when you submit; the form no longer asks you to type it separately (paper 7.01). See defects report and fabrication-detection doc.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>7.03  Tabbatar da lambar ka</t>
+          <t>[HAUSA: sai an fassara ta kwararre — professional translation pending]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>supervisor_note</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>7.02  Observation that may help the office interpret this form</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>7.02  Bayani da zai taimaka wa ofis</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Do not record the respondent's name or other identifying detail here -- see data-protection notes.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Kada a rubuta sunan wanda ake tambaya ko wani bayani da zai bayyana shi a nan.</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
@@ -4713,71 +4821,69 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one enumerator</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>s7sup</t>
+          <t>supervisor_signoff_enum_code</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Supervisor review (completed after handover, not by the enumerator)</t>
+          <t>7.03  Enumerator signature (select your code again to confirm)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bitar mai kula</t>
+          <t>7.03  Tabbatar da lambar ka</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>field-list</t>
+          <t>minimal</t>
         </is>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>select_one enumerator</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>supervisor_code</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>7.04  Supervisor code</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>7.04  Lambar mai kula</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
@@ -4787,34 +4893,31 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_one supervisor_decision</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>supervisor_decision</t>
+          <t>s7sup</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.05  Supervisor decision on this form</t>
+          <t>Supervisor review (completed after handover, not by the enumerator)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7.05  Shawarar mai kula</t>
+          <t>Bitar mai kula</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -4828,22 +4931,35 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t>minimal</t>
+          <t>field-list</t>
         </is>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
+          <t>select_one enumerator</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>supervisor_code</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>7.04  Supervisor code</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>7.04  Lambar mai kula</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
@@ -4853,10 +4969,79 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>select_one supervisor_decision</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>supervisor_decision</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>7.05  Supervisor decision on this form</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>7.05  Shawarar mai kula</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9265,7 +9450,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026073101</t>
+          <t>2026080101</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -9281,6 +9466,66 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>theme-grid</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>entity_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>create_if</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>update_if</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>used_specimen_labels</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>${specimen_obtained}='1' and string-length(${specimen_label}) &gt; 0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>${specimen_label}</t>
         </is>
       </c>
     </row>
